--- a/4.7.2 эффект поккельса/2026/данные.xlsx
+++ b/4.7.2 эффект поккельса/2026/данные.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\бакалавриат\4 semester\оптика\лабы\эффект поккельса\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\бакалавриат\4 semester (try 2)\лабы\4.7.2 эффект поккельса\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="параметры" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>lambda, мкм</t>
   </si>
@@ -79,16 +79,67 @@
     <t>длина кристалла</t>
   </si>
   <si>
-    <t>взять из фотки</t>
-  </si>
-  <si>
     <t>расстояние до ближайшего к лазеру края кристалла от экрана</t>
+  </si>
+  <si>
+    <t>r_min, pix</t>
+  </si>
+  <si>
+    <t>k, cm/pix</t>
+  </si>
+  <si>
+    <t>delta r, pix</t>
+  </si>
+  <si>
+    <t>r_max, pix</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>всякая страшная обработка</t>
+  </si>
+  <si>
+    <t>U_перп, В</t>
+  </si>
+  <si>
+    <t>U_пар, В</t>
+  </si>
+  <si>
+    <t>delta_U_пар, В</t>
+  </si>
+  <si>
+    <t>U, В</t>
+  </si>
+  <si>
+    <t>выборка полуволнового напряжения на глаз</t>
+  </si>
+  <si>
+    <t>delta_U, В</t>
+  </si>
+  <si>
+    <t>U_ср, В</t>
+  </si>
+  <si>
+    <t>статист погр</t>
+  </si>
+  <si>
+    <t>приборная погр</t>
+  </si>
+  <si>
+    <t>суммарная погрешность</t>
+  </si>
+  <si>
+    <t>выборка полуволнового напряжения по фотодатчику</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -119,9 +170,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -450,7 +503,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -463,10 +516,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
@@ -475,26 +528,29 @@
     <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="4"/>
       <c r="F1" t="s">
         <v>7</v>
       </c>
       <c r="G1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -516,8 +572,12 @@
       <c r="G2">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I2">
+        <f>1.5/100*1000</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -540,7 +600,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -563,15 +623,452 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <f>1.5 /100*B2</f>
+        <v>0.36</v>
+      </c>
+      <c r="C7">
+        <f>1.5 /100*C2</f>
+        <v>0.54</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:G7" si="0">1.5 /100*D2</f>
+        <v>0.39</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.54</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.435</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <f t="shared" ref="B8:C8" si="1">1.5 /100*B3</f>
+        <v>0.84</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="C8:G8" si="2">1.5 /100*D3</f>
+        <v>0.75</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>1.05</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>0.87</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <f t="shared" ref="B9:C9" si="3">1.5 /100*B4</f>
+        <v>1.26</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="3"/>
+        <v>1.41</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="C9:G9" si="4">1.5 /100*D4</f>
+        <v>1.3199999999999998</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="4"/>
+        <v>1.47</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>1.365</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="4"/>
+        <v>1.365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <f>(B7+C7)/2</f>
+        <v>0.45</v>
+      </c>
+      <c r="C11">
+        <f>(C7-B7)/2</f>
+        <v>9.0000000000000024E-2</v>
+      </c>
+      <c r="D11">
+        <f>(D7+E7)/2</f>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="E11">
+        <f>(E7-D7)/2</f>
+        <v>7.5000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B12">
+        <f t="shared" ref="B12:B13" si="5">(B8+C8)/2</f>
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:C13" si="6">(C8-B8)/2</f>
+        <v>4.4999999999999984E-2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ref="D12:D13" si="7">(D8+E8)/2</f>
+        <v>0.9</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:E13" si="8">(E8-D8)/2</f>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13">
+        <f t="shared" si="5"/>
+        <v>1.335</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="6"/>
+        <v>7.4999999999999956E-2</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="7"/>
+        <v>1.395</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="8"/>
+        <v>7.5000000000000067E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="3">
+        <f>B11*1000</f>
+        <v>450</v>
+      </c>
+      <c r="C15" s="3">
+        <f>C11*1000+$I$2</f>
+        <v>105.00000000000003</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" ref="C15:E15" si="9">D11*1000</f>
+        <v>465</v>
+      </c>
+      <c r="E15" s="3">
+        <f>E11*1000+$I$2</f>
+        <v>90.000000000000014</v>
+      </c>
+      <c r="F15" s="3">
+        <f>F7*1000</f>
+        <v>435</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="3">
+        <f t="shared" ref="B16:E16" si="10">B12*1000</f>
+        <v>885</v>
+      </c>
+      <c r="C16" s="3">
+        <f t="shared" ref="C16:C17" si="11">C12*1000+$I$2</f>
+        <v>59.999999999999986</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="10"/>
+        <v>900</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" ref="E16:E17" si="12">E12*1000+$I$2</f>
+        <v>165.00000000000003</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" ref="F16:G16" si="13">F8*1000</f>
+        <v>870</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="3">
+        <f t="shared" ref="B17:E17" si="14">B13*1000</f>
+        <v>1335</v>
+      </c>
+      <c r="C17" s="3">
+        <f t="shared" si="11"/>
+        <v>89.999999999999957</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="14"/>
+        <v>1395</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="12"/>
+        <v>90.000000000000071</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" ref="F17:G17" si="15">F9*1000</f>
+        <v>1365</v>
+      </c>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="3">
+        <f>B15</f>
+        <v>450</v>
+      </c>
+      <c r="C21" s="3">
+        <f>C15</f>
+        <v>105.00000000000003</v>
+      </c>
+      <c r="D21" s="3">
+        <f>AVERAGE(B21:B26)</f>
+        <v>452.91666666666669</v>
+      </c>
+      <c r="E21">
+        <f>_xlfn.VAR.S(B21:B26)</f>
+        <v>96.041666666666671</v>
+      </c>
+      <c r="F21">
+        <v>28</v>
+      </c>
+      <c r="G21">
+        <f>SQRT(F21*F21+E22*E22)</f>
+        <v>29.665496231593139</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <f>B16/2</f>
+        <v>442.5</v>
+      </c>
+      <c r="C22">
+        <f>C16/2</f>
+        <v>29.999999999999993</v>
+      </c>
+      <c r="E22">
+        <f>SQRT(E21)</f>
+        <v>9.8000850336446916</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <f>B17/3</f>
+        <v>445</v>
+      </c>
+      <c r="C23">
+        <f>C17/3</f>
+        <v>29.999999999999986</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="3">
+        <f>D15</f>
+        <v>465</v>
+      </c>
+      <c r="C24" s="3">
+        <f>E15</f>
+        <v>90.000000000000014</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <f>D16/2</f>
+        <v>450</v>
+      </c>
+      <c r="C25">
+        <f>E16/2</f>
+        <v>82.500000000000014</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26">
+        <f>D17/3</f>
+        <v>465</v>
+      </c>
+      <c r="C26">
+        <f>E17/3</f>
+        <v>30.000000000000025</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="3">
+        <f>F15</f>
+        <v>435</v>
+      </c>
+      <c r="C30">
+        <f>15</f>
+        <v>15</v>
+      </c>
+      <c r="D30" s="3">
+        <f>AVERAGE(B30:B35)</f>
+        <v>441.66666666666669</v>
+      </c>
+      <c r="E30">
+        <f>_xlfn.VAR.S(B30:B35)</f>
+        <v>106.66666666666666</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <f>SQRT(E31*E31+F30*F30)</f>
+        <v>11.075498483890765</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31">
+        <f>F16/2</f>
+        <v>435</v>
+      </c>
+      <c r="C31">
+        <f>15/2</f>
+        <v>7.5</v>
+      </c>
+      <c r="E31">
+        <f>SQRT(E30)</f>
+        <v>10.327955589886445</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32">
+        <f>F17/3</f>
+        <v>455</v>
+      </c>
+      <c r="C32">
+        <f>15/3</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B33" s="3">
+        <f>F15</f>
+        <v>435</v>
+      </c>
+      <c r="C33">
+        <f>15</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B34">
+        <f>F16/2</f>
+        <v>435</v>
+      </c>
+      <c r="C34">
+        <f>15/2</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <f>F17/3</f>
+        <v>455</v>
+      </c>
+      <c r="C35">
+        <f>15/3</f>
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -579,76 +1076,223 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="3">
+        <v>131</v>
+      </c>
+      <c r="C2">
+        <v>156</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <f>15.5/830</f>
+        <v>1.8674698795180723E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <f>$E$2*B2</f>
+        <v>2.4463855421686747</v>
+      </c>
+      <c r="G2" s="2">
+        <f>$E$2*C2</f>
+        <v>2.9132530120481928</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2*E2</f>
+        <v>9.337349397590361E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>192</v>
+      </c>
+      <c r="C3">
+        <v>213</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F10" si="0">$E$2*B3</f>
+        <v>3.5855421686746989</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G10" si="1">$E$2*C3</f>
+        <v>3.9777108433734942</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>240</v>
+      </c>
+      <c r="C4">
+        <v>256</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>4.4819277108433733</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
+        <v>4.7807228915662652</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <v>278</v>
+      </c>
+      <c r="C5">
+        <v>292</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>5.1915662650602412</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>5.4530120481927709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>312</v>
+      </c>
+      <c r="C6">
+        <v>326</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>5.8265060240963855</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>6.087951807228916</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>341</v>
+      </c>
+      <c r="C7">
+        <v>355</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>6.3680722891566264</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>6.6295180722891569</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>370</v>
+      </c>
+      <c r="C8">
+        <v>380</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>6.9096385542168672</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>7.096385542168675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>397</v>
+      </c>
+      <c r="C9">
+        <v>408</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>7.4138554216867476</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>7.6192771084337352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
+      </c>
+      <c r="B10">
+        <v>420</v>
+      </c>
+      <c r="C10">
+        <v>429</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>7.8433734939759034</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>8.0114457831325296</v>
       </c>
     </row>
   </sheetData>
